--- a/artfynd/S 1761-2022 artfynd.xlsx
+++ b/artfynd/S 1761-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY62"/>
+  <dimension ref="A1:AZ62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
           <t>Inventering av Mittlandet 2022</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103896192</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
           <t>Inventering av Mittlandet 2022</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103896179</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105292278</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1086,6 +1106,11 @@
       <c r="AY5" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/415225</t>
         </is>
       </c>
     </row>
@@ -1204,6 +1229,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78533995</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1305,6 +1335,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6802438</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1418,6 +1453,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86848843</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1533,6 +1573,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/849583</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1633,6 +1678,11 @@
       <c r="AY10" t="inlineStr">
         <is>
           <t>Svampinventeringar i Mittlandet 2018-2021</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95879469</t>
         </is>
       </c>
     </row>
@@ -1775,6 +1825,11 @@
           <t>Inventering av Mittlandet 2022</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103896342</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1886,6 +1941,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114530235</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2011,6 +2071,11 @@
           <t>Mittlandets fåglar</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112066696</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2126,6 +2191,11 @@
           <t>Inventering av långbensgroda</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62369783</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2248,6 +2318,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54827069</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2359,6 +2434,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57815055</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2473,6 +2553,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70551107</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2588,6 +2673,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76622327</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2698,6 +2788,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57815064</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2820,6 +2915,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100956901</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2931,6 +3031,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/15158454</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3053,6 +3158,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54827050</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3183,6 +3293,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/15158461</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3305,6 +3420,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54827125</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3402,6 +3522,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82661679</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3518,6 +3643,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/77827579</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3645,6 +3775,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/15572553</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3766,6 +3901,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120728878</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3880,6 +4020,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76534328</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4001,6 +4146,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14677546</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4126,6 +4276,11 @@
           <t>Mittlandets fåglar</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112066649</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4251,6 +4406,11 @@
           <t>Mittlandets fåglar</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112066652</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4367,6 +4527,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14309982</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4493,6 +4658,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131123791</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4604,6 +4774,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/15158455</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4726,6 +4901,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54827029</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4836,6 +5016,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70551150</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4955,6 +5140,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76622316</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5075,6 +5265,11 @@
           <t>Inventering av långbensgroda</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/59178540</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5186,6 +5381,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76692430</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5306,6 +5506,11 @@
           <t>Inventering av långbensgroda</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/59178541</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5426,6 +5631,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2223976</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5535,6 +5745,11 @@
       <c r="AY43" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2223986</t>
         </is>
       </c>
     </row>
@@ -5646,6 +5861,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66407579</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5752,6 +5972,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125276755</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5861,6 +6086,11 @@
       <c r="AY46" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2643612</t>
         </is>
       </c>
     </row>
@@ -5970,6 +6200,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93709194</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6067,6 +6302,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105286383</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6170,6 +6410,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86849556</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6273,6 +6518,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86849548</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6374,6 +6624,11 @@
           <t>Inventering av Ölands kärlväxtflora., Uppföljning av kärlväxter i gräsmarker i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90968120</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6471,6 +6726,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105287585</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6568,6 +6828,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105287586</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6686,6 +6951,11 @@
       <c r="AY54" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4005130</t>
         </is>
       </c>
     </row>
@@ -6797,6 +7067,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66238440</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6915,6 +7190,11 @@
       <c r="AY56" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3790008</t>
         </is>
       </c>
     </row>
@@ -7019,6 +7299,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110785268</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7125,6 +7410,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5791418</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7231,6 +7521,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100964683</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7348,6 +7643,11 @@
           <t>Inventering av Ölands kärlväxtflora., Arkiv Floraväktarlokaler</t>
         </is>
       </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66384570</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7479,6 +7779,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92693502</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7619,8 +7924,76 @@
           <t>Inventering av Mittlandet 2022</t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103896341</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>